--- a/buildplan_generator/output/25-083 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-083 GENERATED BUILD PLAN.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-062, 23-040, 25-074, 23-018, 25-085</t>
+          <t>23-055, 25-055, 25-077, 23-023, 26-016</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>4.2</v>
+      <c r="F9" s="9" t="n">
+        <v>16.8</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.5</t>
+          <t>ratio=1.40 (0.92-2.20)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>8</v>
+      <c r="F10" s="9" t="n">
+        <v>24.2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>4.0-21.5</t>
+          <t>ratio=1.34 (0.42-2.31)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -796,17 +794,17 @@
       <c r="E11" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="9" t="n">
         <v>4</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=1.00 (0.40-1.00)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -833,8 +831,8 @@
       <c r="E12" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="9" t="n">
-        <v>11</v>
+      <c r="F12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -843,7 +841,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>global:3.0-31.8</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -870,17 +868,17 @@
       <c r="E13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>2</v>
+      <c r="F13" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -907,8 +905,8 @@
       <c r="E14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>2</v>
+      <c r="F14" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -917,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.25 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -944,8 +942,8 @@
       <c r="E15" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>5</v>
+      <c r="F15" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -954,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>4.0-7.0</t>
+          <t>ratio=1.25 (0.80-1.25)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -998,8 +996,8 @@
       <c r="E17" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>39.5</v>
+      <c r="F17" s="9" t="n">
+        <v>35.4</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1008,7 +1006,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>25.5-59.5</t>
+          <t>ratio=1.77 (1.42-2.44)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1035,17 +1033,17 @@
       <c r="E18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="10" t="n">
-        <v>16</v>
+      <c r="F18" s="11" t="n">
+        <v>13.8</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>9.5-20.5</t>
+          <t>ratio=1.15 (n=2)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1089,8 +1087,8 @@
       <c r="E20" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>6</v>
+      <c r="F20" s="9" t="n">
+        <v>21.7</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1099,7 +1097,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>3.5-46.5</t>
+          <t>ratio=1.08 (1.00-1.38)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1143,7 +1141,7 @@
       <c r="E22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -1153,7 +1151,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1181,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1190,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=0.61 (n=2)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1235,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1244,7 +1242,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1272,12 +1270,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1304,8 +1302,8 @@
       <c r="E27" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>15</v>
+      <c r="F27" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1314,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>3.0-33.0</t>
+          <t>ratio=1.00 (0.67-1.05)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1341,17 +1339,17 @@
       <c r="E28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>12</v>
+      <c r="F28" s="11" t="n">
+        <v>6.6</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>4.0-17.0</t>
+          <t>ratio=1.32 (n=2)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1393,17 +1391,15 @@
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
-      <c r="F30" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1430,8 +1426,8 @@
       <c r="E31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>4</v>
+      <c r="F31" s="9" t="n">
+        <v>2.6</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1440,7 +1436,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>ratio=1.30 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1467,8 +1463,8 @@
       <c r="E32" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>4</v>
+      <c r="F32" s="9" t="n">
+        <v>25.7</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1477,7 +1473,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>2.0-8.2</t>
+          <t>ratio=1.83 (1.50-5.00)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1504,8 +1500,8 @@
       <c r="E33" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>7.5</v>
+      <c r="F33" s="9" t="n">
+        <v>14.7</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1514,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>6.5-26.0</t>
+          <t>ratio=0.61 (0.31-1.05)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1541,17 +1537,17 @@
       <c r="E34" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F34" s="11" t="n">
-        <v>7</v>
+      <c r="F34" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>ratio=0.75 (0.62-1.33)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1579,7 +1575,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1588,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>5.0-5.0</t>
+          <t>ratio=1.04 (n=2)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1615,8 +1611,8 @@
       <c r="E36" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>4</v>
+      <c r="F36" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1625,7 +1621,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>global:2.5-5.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1670,7 +1666,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=2.62 (n=2)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1706,17 +1702,17 @@
       <c r="E39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="11" t="n">
-        <v>2.5</v>
+      <c r="F39" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1743,8 +1739,8 @@
       <c r="E40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>1.5</v>
+      <c r="F40" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1753,7 +1749,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1781,7 +1777,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>39.2</v>
+        <v>18.3</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1790,7 +1786,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>16.5-62.0</t>
+          <t>ratio=0.92 (n=2)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1818,7 +1814,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>45</v>
+        <v>33.3</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1827,7 +1823,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>28.5-61.5</t>
+          <t>ratio=1.39 (n=2)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1855,7 +1851,7 @@
         <v>8</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1864,7 +1860,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>7.0-7.0</t>
+          <t>ratio=0.20 (n=1)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1891,17 +1887,17 @@
       <c r="E44" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1946,12 +1942,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1978,8 +1974,8 @@
       <c r="E47" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>8.5</v>
+      <c r="F47" s="9" t="n">
+        <v>6.4</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1988,7 +1984,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>6.5-15.0</t>
+          <t>ratio=0.92 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2015,8 +2011,8 @@
       <c r="E48" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>3</v>
+      <c r="F48" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2025,7 +2021,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>1.5-5.0</t>
+          <t>ratio=1.00 (1.00-1.81)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2052,8 +2048,8 @@
       <c r="E49" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F49" s="9" t="n">
-        <v>29</v>
+      <c r="F49" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2062,7 +2058,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>global:6.0-52.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2087,17 +2083,15 @@
         </is>
       </c>
       <c r="E50" s="8" t="n"/>
-      <c r="F50" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2124,8 +2118,8 @@
       <c r="E51" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>8</v>
+      <c r="F51" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2134,7 +2128,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>4.0-12.0</t>
+          <t>ratio=2.50 (1.00-2.50)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2161,17 +2155,17 @@
       <c r="E52" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F52" s="11" t="n">
-        <v>6</v>
+      <c r="F52" s="9" t="n">
+        <v>5.3</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>4.0-8.0</t>
+          <t>ratio=0.67 (0.42-1.06)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2198,17 +2192,17 @@
       <c r="E53" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F53" s="10" t="n">
-        <v>24</v>
+      <c r="F53" s="11" t="n">
+        <v>13.3</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>15.5-34.5</t>
+          <t>ratio=2.22 (n=2)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2235,8 +2229,8 @@
       <c r="E54" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F54" s="10" t="n">
-        <v>4.5</v>
+      <c r="F54" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>2.0-7.0</t>
+          <t>ratio=2.50 (2.00-3.00)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2290,7 +2284,7 @@
         <v>60</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>54.4</v>
+        <v>43.8</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2299,7 +2293,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>53.8-55.0</t>
+          <t>ratio=0.73 (n=2)</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2327,7 +2321,7 @@
         <v>30</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>64.5</v>
+        <v>49.3</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2336,7 +2330,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>56.2-72.8</t>
+          <t>ratio=1.64 (n=2)</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2364,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2373,7 +2367,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>2.0-6.0</t>
+          <t>ratio=0.62 (n=2)</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2400,17 +2394,17 @@
       <c r="E59" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F59" s="9" t="n">
-        <v>2.8</v>
+      <c r="F59" s="11" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-6.5</t>
+          <t>ratio=1.03 (n=2)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2437,17 +2431,17 @@
       <c r="E60" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F60" s="10" t="n">
-        <v>21.8</v>
+      <c r="F60" s="11" t="n">
+        <v>13.1</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>9.0-102.0</t>
+          <t>ratio=1.09 (n=2)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2474,8 +2468,8 @@
       <c r="E61" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F61" s="10" t="n">
-        <v>25.2</v>
+      <c r="F61" s="9" t="n">
+        <v>12.5</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2484,7 +2478,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>17.0-44.0</t>
+          <t>ratio=0.62 (0.47-1.10)</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2511,17 +2505,17 @@
       <c r="E62" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="10" t="n">
-        <v>5</v>
+      <c r="F62" s="11" t="n">
+        <v>1.2</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>2.0-7.5</t>
+          <t>ratio=0.60 (n=2)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2548,17 +2542,17 @@
       <c r="E63" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F63" s="10" t="n">
-        <v>7.5</v>
+      <c r="F63" s="11" t="n">
+        <v>2.5</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>3.0-10.0</t>
+          <t>ratio=0.41 (n=2)</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2585,8 +2579,8 @@
       <c r="E64" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F64" s="9" t="n">
-        <v>4.5</v>
+      <c r="F64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2595,7 +2589,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-24.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2622,8 +2616,8 @@
       <c r="E65" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="9" t="n">
-        <v>8.800000000000001</v>
+      <c r="F65" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2632,7 +2626,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>global:2.5-118.8</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2659,7 +2653,7 @@
       <c r="E66" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="10" t="n">
+      <c r="F66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -2669,7 +2663,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>0.2-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2713,17 +2707,17 @@
       <c r="E68" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="10" t="n">
-        <v>1</v>
+      <c r="F68" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>1.0-25.0</t>
+          <t>ratio=2.00 (n=1)</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2748,17 +2742,15 @@
         </is>
       </c>
       <c r="E69" s="8" t="n"/>
-      <c r="F69" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2786,12 +2778,12 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2835,8 +2827,8 @@
       <c r="E72" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F72" s="10" t="n">
-        <v>3</v>
+      <c r="F72" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
@@ -2845,7 +2837,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>1.0-10.0</t>
+          <t>ratio=1.00 (1.00-4.00)</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2872,8 +2864,8 @@
       <c r="E73" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F73" s="10" t="n">
-        <v>21</v>
+      <c r="F73" s="9" t="n">
+        <v>44.2</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2882,7 +2874,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>7.0-42.0</t>
+          <t>ratio=1.47 (0.90-2.33)</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2910,12 +2902,12 @@
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2943,12 +2935,12 @@
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2975,17 +2967,17 @@
       <c r="E76" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="F76" s="10" t="n">
-        <v>40</v>
+      <c r="F76" s="11" t="n">
+        <v>67</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>25.5-68.5</t>
+          <t>ratio=1.86 (n=2)</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -3013,12 +3005,12 @@
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I77" s="8" t="n"/>
@@ -3062,8 +3054,8 @@
       <c r="E79" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F79" s="10" t="n">
-        <v>8</v>
+      <c r="F79" s="9" t="n">
+        <v>12</v>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
@@ -3072,7 +3064,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>5.0-20.0</t>
+          <t>ratio=4.00 (2.17-5.00)</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3100,12 +3092,12 @@
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I80" s="8" t="n"/>
@@ -3132,8 +3124,8 @@
       <c r="E81" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F81" s="10" t="n">
-        <v>9.199999999999999</v>
+      <c r="F81" s="9" t="n">
+        <v>14.2</v>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
@@ -3142,7 +3134,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>7.5-17.0</t>
+          <t>ratio=2.38 (1.50-3.00)</t>
         </is>
       </c>
       <c r="I81" s="8" t="n"/>
@@ -3156,7 +3148,7 @@
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>633.1</v>
+        <v>612.9</v>
       </c>
     </row>
   </sheetData>
@@ -3224,7 +3216,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-062, 23-040, 25-074, 23-018, 25-085</t>
+          <t>23-055, 25-055, 25-077, 23-023, 26-016</t>
         </is>
       </c>
     </row>
@@ -5237,35 +5229,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-062</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-040</t>
+          <t>25-055</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-074</t>
+          <t>25-077</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-018</t>
+          <t>23-023</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-085</t>
+          <t>26-016</t>
         </is>
       </c>
     </row>
@@ -5320,23 +5312,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5354,19 +5342,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>23-018, 23-040, 24-062, 25-085</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5380,7 +5364,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.2</v>
+        <v>16.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5389,12 +5373,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.0-5.5</t>
+          <t>ratio=1.40 (0.92-2.20)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5394,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>24.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5419,12 +5403,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.0-21.5</t>
+          <t>ratio=1.34 (0.42-2.31)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5444,17 +5428,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=1.00 (0.40-1.00)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-085, 23-018</t>
+          <t>25-077, 25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5454,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5479,12 +5463,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>global:3.0-31.8</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -5500,21 +5484,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5514,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5539,12 +5523,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.25 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5544,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5569,12 +5553,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4.0-7.0</t>
+          <t>ratio=1.25 (0.80-1.25)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5574,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>39.5</v>
+        <v>35.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5599,12 +5583,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25.5-59.5</t>
+          <t>ratio=1.77 (1.42-2.44)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5620,21 +5604,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
+        <v>13.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9.5-20.5</t>
+          <t>ratio=1.15 (n=2)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062</t>
+          <t>25-077, 25-055</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5634,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>21.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5659,12 +5643,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.5-46.5</t>
+          <t>ratio=1.08 (1.00-1.38)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5689,12 +5673,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5694,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5719,12 +5703,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=0.61 (n=2)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>24-062</t>
+          <t>25-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5724,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5749,12 +5733,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-074</t>
+          <t>23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5774,19 +5758,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>23-018, 23-040, 24-062, 25-074, 25-085</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5800,7 +5780,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5809,12 +5789,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.0-33.0</t>
+          <t>ratio=1.00 (0.67-1.05)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5830,21 +5810,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4.0-17.0</t>
+          <t>ratio=1.32 (n=2)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5860,23 +5840,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5890,7 +5866,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5899,12 +5875,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.0-12.0</t>
+          <t>ratio=1.30 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5896,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>25.7</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5929,12 +5905,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2.0-8.2</t>
+          <t>ratio=1.83 (1.50-5.00)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5926,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7.5</v>
+        <v>14.7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5959,12 +5935,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6.5-26.0</t>
+          <t>ratio=0.61 (0.31-1.05)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 25-055, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -5980,21 +5956,21 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6.0-8.0</t>
+          <t>ratio=0.75 (0.62-1.33)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-085, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6010,7 +5986,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6019,12 +5995,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5.0-5.0</t>
+          <t>ratio=1.04 (n=2)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23-018</t>
+          <t>23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6016,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6049,12 +6025,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>global:2.5-5.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6070,23 +6046,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6100,7 +6072,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6109,12 +6081,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=2.62 (n=2)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-074, 24-062, 23-018</t>
+          <t>25-077, 23-023</t>
         </is>
       </c>
     </row>
@@ -6130,21 +6102,21 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-074, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6132,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6169,12 +6141,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-074, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6162,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>39.2</v>
+        <v>18.3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6199,12 +6171,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16.5-62.0</t>
+          <t>ratio=0.92 (n=2)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>23-040, 23-018</t>
+          <t>25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6192,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>45</v>
+        <v>33.3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6229,12 +6201,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>28.5-61.5</t>
+          <t>ratio=1.39 (n=2)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>23-040, 23-018</t>
+          <t>25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6222,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6259,12 +6231,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.0-7.0</t>
+          <t>ratio=0.20 (n=1)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>23-040, 23-018</t>
+          <t>25-077</t>
         </is>
       </c>
     </row>
@@ -6284,15 +6256,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>no data</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>wc_ratio=1.00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>wc_avg</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6310,19 +6286,15 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>23-018, 24-062, 25-085</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6336,7 +6308,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6345,12 +6317,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6.5-15.0</t>
+          <t>ratio=0.92 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6338,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6375,12 +6347,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5-5.0</t>
+          <t>ratio=1.00 (1.00-1.81)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6368,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6405,12 +6377,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>global:6.0-52.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6426,23 +6398,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6456,7 +6424,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6465,12 +6433,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4.0-12.0</t>
+          <t>ratio=2.50 (1.00-2.50)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6486,21 +6454,21 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4.0-8.0</t>
+          <t>ratio=0.67 (0.42-1.06)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-074, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6516,21 +6484,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>24</v>
+        <v>13.3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15.5-34.5</t>
+          <t>ratio=2.22 (n=2)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6514,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6555,12 +6523,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2.0-7.0</t>
+          <t>ratio=2.50 (2.00-3.00)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6544,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54.4</v>
+        <v>43.8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,12 +6553,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>53.8-55.0</t>
+          <t>ratio=0.73 (n=2)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>23-040, 23-018</t>
+          <t>25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6574,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>64.5</v>
+        <v>49.3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6615,12 +6583,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>56.2-72.8</t>
+          <t>ratio=1.64 (n=2)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>23-040, 23-018</t>
+          <t>25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6604,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6645,12 +6613,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2.0-6.0</t>
+          <t>ratio=0.62 (n=2)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>23-040, 23-018</t>
+          <t>25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -6666,21 +6634,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>global:1.0-6.5</t>
+          <t>ratio=1.03 (n=2)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-077, 23-055</t>
         </is>
       </c>
     </row>
@@ -6696,21 +6664,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>21.8</v>
+        <v>13.1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>9.0-102.0</t>
+          <t>ratio=1.09 (n=2)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-085, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-023</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6694,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>25.2</v>
+        <v>12.5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6735,12 +6703,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17.0-44.0</t>
+          <t>ratio=0.62 (0.47-1.10)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6756,21 +6724,21 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2.0-7.5</t>
+          <t>ratio=0.60 (n=2)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-023</t>
         </is>
       </c>
     </row>
@@ -6786,21 +6754,21 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>3.0-10.0</t>
+          <t>ratio=0.41 (n=2)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-023</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6784,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6825,12 +6793,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>global:0.5-24.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6814,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6855,12 +6823,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>global:2.5-118.8</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6853,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.2-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -6906,21 +6874,21 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.0-25.0</t>
+          <t>ratio=2.00 (n=1)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>23-023</t>
         </is>
       </c>
     </row>
@@ -6936,23 +6904,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6970,19 +6934,15 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>23-018, 24-062, 25-085</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6996,7 +6956,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7005,12 +6965,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.0-10.0</t>
+          <t>ratio=1.00 (1.00-4.00)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -7026,7 +6986,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>21</v>
+        <v>44.2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7035,12 +6995,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7.0-42.0</t>
+          <t>ratio=1.47 (0.90-2.33)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -7060,19 +7020,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>23-018, 23-040, 24-062, 25-074, 25-085</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7090,19 +7046,15 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>23-018, 24-062, 25-085</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7116,21 +7068,21 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>25.5-68.5</t>
+          <t>ratio=1.86 (n=2)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-023</t>
         </is>
       </c>
     </row>
@@ -7150,19 +7102,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>23-018, 23-040, 24-062, 25-074, 25-085</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7176,7 +7124,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7185,12 +7133,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5.0-20.0</t>
+          <t>ratio=4.00 (2.17-5.00)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>
@@ -7210,19 +7158,15 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>23-018, 23-040, 24-062, 25-074, 25-085</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7236,7 +7180,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7245,12 +7189,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>7.5-17.0</t>
+          <t>ratio=2.38 (1.50-3.00)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>25-085, 25-074, 24-062, 23-040, 23-018</t>
+          <t>25-077, 23-055, 23-023</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-083 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-083 GENERATED BUILD PLAN.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-055, 25-055, 25-077, 23-023, 26-016</t>
+          <t>23-055, 25-055, 25-077, 25-039, 25-111</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>16.8</v>
+        <v>14.9</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.40 (0.92-2.20)</t>
+          <t>ratio=1.24 (0.92-2.20)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>24.2</v>
+        <v>14</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.34 (0.42-2.31)</t>
+          <t>ratio=0.78 (0.29-2.31)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -906,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-1.50)</t>
+          <t>ratio=1.00 (1.00-1.25)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.80-1.25)</t>
+          <t>ratio=1.25 (1.00-1.25)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -997,7 +997,7 @@
         <v>20</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>35.4</v>
+        <v>28.3</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.77 (1.42-2.44)</t>
+          <t>ratio=1.42 (0.40-2.44)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1033,17 +1033,17 @@
       <c r="E18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="9" t="n">
         <v>13.8</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.15 (n=2)</t>
+          <t>ratio=1.15 (0.75-1.55)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1088,7 +1088,7 @@
         <v>20</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>21.7</v>
+        <v>21</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.08 (1.00-1.38)</t>
+          <t>ratio=1.05 (1.00-1.38)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.61 (n=2)</t>
+          <t>ratio=0.53 (n=2)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1233,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>ratio=1.25 (n=2)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.05)</t>
+          <t>ratio=1.00 (0.67-1.50)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1339,17 +1339,17 @@
       <c r="E28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>6.6</v>
+      <c r="F28" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.32 (n=2)</t>
+          <t>ratio=1.00 (0.62-1.75)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1427,7 +1427,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.30 (1.00-2.00)</t>
+          <t>ratio=1.57 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1464,7 +1464,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>25.7</v>
+        <v>21</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.83 (1.50-5.00)</t>
+          <t>ratio=1.50 (0.50-1.83)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1501,7 +1501,7 @@
         <v>24</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>14.7</v>
+        <v>14.2</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.31-1.05)</t>
+          <t>ratio=0.59 (0.31-1.05)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1538,7 +1538,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.62-1.33)</t>
+          <t>ratio=0.67 (0.62-0.75)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1575,7 +1575,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.04 (n=2)</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1666,7 +1666,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.62 (n=2)</t>
+          <t>ratio=2.00 (n=2)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>ratio=1.00 (0.67-1.00)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.50-1.00)</t>
+          <t>ratio=0.50 (0.38-0.92)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.81)</t>
+          <t>ratio=1.00 (0.83-1.00)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2049,7 +2049,7 @@
         <v>15</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>wc_ratio=0.82</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2119,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.00-2.50)</t>
+          <t>ratio=1.00 (0.75-2.50)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2156,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.42-1.06)</t>
+          <t>ratio=0.57 (0.42-0.67)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2193,7 +2193,7 @@
         <v>6</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>13.3</v>
+        <v>9.5</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.22 (n=2)</t>
+          <t>ratio=1.58 (n=2)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2230,7 +2230,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.50 (2.00-3.00)</t>
+          <t>ratio=2.00 (1.50-2.50)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2432,7 +2432,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>13.1</v>
+        <v>4.8</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.09 (n=2)</t>
+          <t>ratio=0.40 (n=1)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.47-1.10)</t>
+          <t>ratio=0.62 (0.40-1.10)</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2506,7 +2506,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.60 (n=2)</t>
+          <t>ratio=0.35 (n=2)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2543,7 +2543,7 @@
         <v>6</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.41 (n=2)</t>
+          <t>ratio=0.30 (n=2)</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2580,7 +2580,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>wc_ratio=0.82</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2617,7 +2617,7 @@
         <v>3</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>wc_ratio=0.82</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2707,17 +2707,17 @@
       <c r="E68" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="11" t="n">
-        <v>2</v>
+      <c r="F68" s="10" t="n">
+        <v>0.8</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=1)</t>
+          <t>wc_ratio=0.82</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-4.00)</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2865,7 +2865,7 @@
         <v>30</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>44.2</v>
+        <v>52</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.47 (0.90-2.33)</t>
+          <t>ratio=1.73 (0.90-2.33)</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2968,7 +2968,7 @@
         <v>36</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>67</v>
+        <v>34.2</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.86 (n=2)</t>
+          <t>ratio=0.95 (n=2)</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>ratio=4.00 (2.17-5.00)</t>
+          <t>ratio=4.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3125,7 +3125,7 @@
         <v>6</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>14.2</v>
+        <v>12</v>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.38 (1.50-3.00)</t>
+          <t>ratio=2.00 (1.50-3.00)</t>
         </is>
       </c>
       <c r="I81" s="8" t="n"/>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>612.9</v>
+        <v>530.7</v>
       </c>
     </row>
   </sheetData>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-055, 25-055, 25-077, 23-023, 26-016</t>
+          <t>23-055, 25-055, 25-077, 25-039, 25-111</t>
         </is>
       </c>
     </row>
@@ -5250,14 +5250,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-023</t>
+          <t>25-039</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26-016</t>
+          <t>25-111</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.8</v>
+        <v>14.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5373,12 +5373,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.40 (0.92-2.20)</t>
+          <t>ratio=1.24 (0.92-2.20)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 23-055, 23-023</t>
+          <t>25-077, 25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.2</v>
+        <v>14</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5403,12 +5403,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.34 (0.42-2.31)</t>
+          <t>ratio=0.78 (0.29-2.31)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 23-055, 23-023</t>
+          <t>25-077, 25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 23-055, 23-023</t>
+          <t>25-077, 25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23-055, 23-023</t>
+          <t>25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-1.50)</t>
+          <t>ratio=1.00 (1.00-1.25)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-055, 23-055, 23-023</t>
+          <t>25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.80-1.25)</t>
+          <t>ratio=1.25 (1.00-1.25)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-055, 23-055, 23-023</t>
+          <t>25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35.4</v>
+        <v>28.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5583,12 +5583,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.77 (1.42-2.44)</t>
+          <t>ratio=1.42 (0.40-2.44)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 23-055, 23-023</t>
+          <t>25-111, 25-077, 25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5608,17 +5608,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.15 (n=2)</t>
+          <t>ratio=1.15 (0.75-1.55)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-077, 25-055</t>
+          <t>25-111, 25-077, 25-055, 25-039</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.7</v>
+        <v>21</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5643,12 +5643,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=1.08 (1.00-1.38)</t>
+          <t>ratio=1.05 (1.00-1.38)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 23-055, 23-023</t>
+          <t>25-077, 25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-055, 23-055, 23-023</t>
+          <t>25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5703,12 +5703,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=0.61 (n=2)</t>
+          <t>ratio=0.53 (n=2)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-055, 23-023</t>
+          <t>25-055, 25-039</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>ratio=1.25 (n=2)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>23-055, 23-023</t>
+          <t>25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.05)</t>
+          <t>ratio=1.00 (0.67-1.50)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-055, 23-055, 23-023</t>
+          <t>25-111, 25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5810,21 +5810,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=1.32 (n=2)</t>
+          <t>ratio=1.00 (0.62-1.75)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>23-055, 23-023</t>
+          <t>25-111, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.30 (1.00-2.00)</t>
+          <t>ratio=1.57 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 23-055, 23-023</t>
+          <t>25-077, 25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25.7</v>
+        <v>21</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5905,12 +5905,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.83 (1.50-5.00)</t>
+          <t>ratio=1.50 (0.50-1.83)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14.7</v>
+        <v>14.2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5935,12 +5935,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.31-1.05)</t>
+          <t>ratio=0.59 (0.31-1.05)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 23-055, 23-023</t>
+          <t>25-077, 25-055, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.62-1.33)</t>
+          <t>ratio=0.67 (0.62-0.75)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5995,12 +5995,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.04 (n=2)</t>
+          <t>ratio=1.50 (n=1)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23-055, 23-023</t>
+          <t>23-055</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6081,12 +6081,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=2.62 (n=2)</t>
+          <t>ratio=2.00 (n=2)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-077, 23-023</t>
+          <t>25-077, 25-039</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.50)</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6141,12 +6141,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>ratio=1.00 (0.67-1.00)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6317,12 +6317,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.50-1.00)</t>
+          <t>ratio=0.50 (0.38-0.92)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6347,12 +6347,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.81)</t>
+          <t>ratio=1.00 (0.83-1.00)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>wc_ratio=0.82</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6433,12 +6433,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.00-2.50)</t>
+          <t>ratio=1.00 (0.75-2.50)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.42-1.06)</t>
+          <t>ratio=0.57 (0.42-0.67)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>13.3</v>
+        <v>9.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6493,12 +6493,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=2.22 (n=2)</t>
+          <t>ratio=1.58 (n=2)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>23-055, 23-023</t>
+          <t>25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6523,12 +6523,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=2.50 (2.00-3.00)</t>
+          <t>ratio=2.00 (1.50-2.50)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13.1</v>
+        <v>4.8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=1.09 (n=2)</t>
+          <t>ratio=0.40 (n=1)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-077, 23-023</t>
+          <t>25-077</t>
         </is>
       </c>
     </row>
@@ -6703,12 +6703,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.47-1.10)</t>
+          <t>ratio=0.62 (0.40-1.10)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6733,12 +6733,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=0.60 (n=2)</t>
+          <t>ratio=0.35 (n=2)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-077, 23-023</t>
+          <t>25-077, 25-039</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=0.41 (n=2)</t>
+          <t>ratio=0.30 (n=2)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-077, 23-023</t>
+          <t>25-077, 25-039</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>wc_ratio=0.82</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>wc_ratio=0.82</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6874,21 +6874,21 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=1)</t>
+          <t>wc_ratio=0.82</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>23-023</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-4.00)</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>44.2</v>
+        <v>52</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ratio=1.47 (0.90-2.33)</t>
+          <t>ratio=1.73 (0.90-2.33)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>67</v>
+        <v>34.2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7077,12 +7077,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ratio=1.86 (n=2)</t>
+          <t>ratio=0.95 (n=2)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>25-077, 23-023</t>
+          <t>25-077, 25-039</t>
         </is>
       </c>
     </row>
@@ -7133,12 +7133,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ratio=4.00 (2.17-5.00)</t>
+          <t>ratio=4.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>14.2</v>
+        <v>12</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7189,12 +7189,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ratio=2.38 (1.50-3.00)</t>
+          <t>ratio=2.00 (1.50-3.00)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>25-077, 23-055, 23-023</t>
+          <t>25-077, 25-039, 23-055</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-083 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-083 GENERATED BUILD PLAN.xlsx
@@ -80,14 +80,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-055, 25-055, 25-077, 25-039, 25-111</t>
+          <t>23-055, 25-055, 25-077, 23-023, 23-015</t>
         </is>
       </c>
     </row>
@@ -638,12 +638,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +721,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>14.9</v>
+        <v>8</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.24 (0.92-2.20)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.29-2.31)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -795,7 +795,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.40-1.00)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -831,17 +831,17 @@
       <c r="E12" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>4</v>
+      <c r="F12" s="9" t="n">
+        <v>3.9</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -868,17 +868,17 @@
       <c r="E13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>1</v>
+      <c r="F13" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -906,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.25)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -943,7 +943,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-1.25)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -997,7 +997,7 @@
         <v>20</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.42 (0.40-2.44)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1034,7 +1034,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>13.8</v>
+        <v>6.8</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.15 (0.75-1.55)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1088,7 +1088,7 @@
         <v>20</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.05 (1.00-1.38)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1142,7 +1142,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1178,17 +1178,17 @@
       <c r="E23" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>1.6</v>
+      <c r="F23" s="9" t="n">
+        <v>6.8</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.53 (n=2)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1232,17 +1232,17 @@
       <c r="E25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="11" t="n">
-        <v>2.5</v>
+      <c r="F25" s="9" t="n">
+        <v>0.4</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (n=2)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1270,12 +1270,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1303,7 +1303,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>6</v>
+        <v>10.8</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.50)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1340,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.75)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1394,12 +1394,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1427,7 +1427,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.57 (1.00-3.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1464,7 +1464,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.50-1.83)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1501,7 +1501,7 @@
         <v>24</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.59 (0.31-1.05)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1538,7 +1538,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.62-0.75)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1574,17 +1574,17 @@
       <c r="E35" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F35" s="11" t="n">
-        <v>7.5</v>
+      <c r="F35" s="9" t="n">
+        <v>4.1</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1611,17 +1611,17 @@
       <c r="E36" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>8</v>
+      <c r="F36" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1665,17 +1665,17 @@
       <c r="E38" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="11" t="n">
-        <v>4</v>
+      <c r="F38" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=2)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1703,7 +1703,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1740,7 +1740,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.00)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1776,17 +1776,17 @@
       <c r="E41" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>18.3</v>
+      <c r="F41" s="9" t="n">
+        <v>7.6</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (n=2)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1813,17 +1813,17 @@
       <c r="E42" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F42" s="11" t="n">
-        <v>33.3</v>
+      <c r="F42" s="9" t="n">
+        <v>7.3</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.39 (n=2)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1850,17 +1850,17 @@
       <c r="E43" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F43" s="11" t="n">
-        <v>1.6</v>
+      <c r="F43" s="9" t="n">
+        <v>1.1</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.20 (n=1)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1888,16 +1888,16 @@
         <v>1</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1942,12 +1942,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>3.5</v>
+        <v>15.7</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.38-0.92)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.00)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2048,17 +2048,17 @@
       <c r="E49" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F49" s="10" t="n">
-        <v>12.3</v>
+      <c r="F49" s="9" t="n">
+        <v>0.4</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.82</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2086,12 +2086,12 @@
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2119,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-2.50)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2156,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.57 (0.42-0.67)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2192,17 +2192,17 @@
       <c r="E53" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F53" s="11" t="n">
-        <v>9.5</v>
+      <c r="F53" s="9" t="n">
+        <v>21.8</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.58 (n=2)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2229,17 +2229,17 @@
       <c r="E54" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F54" s="9" t="n">
-        <v>4</v>
+      <c r="F54" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.50-2.50)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2283,17 +2283,17 @@
       <c r="E56" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F56" s="11" t="n">
-        <v>43.8</v>
+      <c r="F56" s="9" t="n">
+        <v>4.1</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.73 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2320,17 +2320,17 @@
       <c r="E57" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F57" s="11" t="n">
-        <v>49.3</v>
+      <c r="F57" s="9" t="n">
+        <v>5.5</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.64 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2357,17 +2357,17 @@
       <c r="E58" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F58" s="11" t="n">
-        <v>5</v>
+      <c r="F58" s="9" t="n">
+        <v>0.4</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2394,17 +2394,17 @@
       <c r="E59" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F59" s="11" t="n">
-        <v>8.199999999999999</v>
+      <c r="F59" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.03 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2431,17 +2431,17 @@
       <c r="E60" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F60" s="11" t="n">
-        <v>4.8</v>
+      <c r="F60" s="9" t="n">
+        <v>18</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.40 (n=1)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2469,7 +2469,7 @@
         <v>20</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>12.5</v>
+        <v>22.4</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.40-1.10)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2505,17 +2505,17 @@
       <c r="E62" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="11" t="n">
-        <v>0.7</v>
+      <c r="F62" s="9" t="n">
+        <v>11.2</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.35 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2542,17 +2542,17 @@
       <c r="E63" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F63" s="11" t="n">
-        <v>1.8</v>
+      <c r="F63" s="9" t="n">
+        <v>22.2</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.30 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2579,17 +2579,17 @@
       <c r="E64" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F64" s="10" t="n">
-        <v>3.3</v>
+      <c r="F64" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.82</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2616,17 +2616,17 @@
       <c r="E65" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="10" t="n">
-        <v>2.5</v>
+      <c r="F65" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.82</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2654,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2707,17 +2707,17 @@
       <c r="E68" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="10" t="n">
-        <v>0.8</v>
+      <c r="F68" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=0.82</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2745,12 +2745,12 @@
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2778,12 +2778,12 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2828,7 +2828,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2865,7 +2865,7 @@
         <v>30</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>52</v>
+        <v>15.7</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.73 (0.90-2.33)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2902,12 +2902,12 @@
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2935,12 +2935,12 @@
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2967,17 +2967,17 @@
       <c r="E76" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="F76" s="11" t="n">
-        <v>34.2</v>
+      <c r="F76" s="9" t="n">
+        <v>27.1</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.95 (n=2)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -3005,12 +3005,12 @@
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I77" s="8" t="n"/>
@@ -3055,7 +3055,7 @@
         <v>3</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>ratio=4.00 (2.00-5.00)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3092,12 +3092,12 @@
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I80" s="8" t="n"/>
@@ -3125,7 +3125,7 @@
         <v>6</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.50-3.00)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="I81" s="8" t="n"/>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>530.7</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-055, 25-055, 25-077, 25-039, 25-111</t>
+          <t>23-055, 25-055, 25-077, 23-023, 23-015</t>
         </is>
       </c>
     </row>
@@ -5250,14 +5250,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-039</t>
+          <t>23-023</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-111</t>
+          <t>23-015</t>
         </is>
       </c>
     </row>
@@ -5316,15 +5316,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5342,15 +5346,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5364,7 +5372,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14.9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5373,12 +5381,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.24 (0.92-2.20)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 25-039, 23-055</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5402,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5403,12 +5411,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.78 (0.29-2.31)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 25-039, 23-055</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5432,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5433,12 +5441,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.40-1.00)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 25-039, 23-055</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5454,21 +5462,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5484,21 +5492,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-039, 23-055</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5522,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5523,12 +5531,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.25)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-055, 25-039, 23-055</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5552,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5553,12 +5561,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.00-1.25)</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-055, 25-039, 23-055</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5582,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5583,12 +5591,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.42 (0.40-2.44)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-111, 25-077, 25-055, 25-039, 23-055</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5612,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13.8</v>
+        <v>6.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5613,12 +5621,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.15 (0.75-1.55)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-111, 25-077, 25-055, 25-039</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5642,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5643,12 +5651,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=1.05 (1.00-1.38)</t>
+          <t>group_total:11h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 25-039, 23-055</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5672,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5673,12 +5681,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-055, 25-039, 23-055</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5694,21 +5702,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=0.53 (n=2)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-055, 25-039</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5724,21 +5732,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.25 (n=2)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-039, 23-055</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5758,15 +5766,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5780,7 +5792,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>10.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5789,12 +5801,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.50)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-111, 25-055, 25-039, 23-055</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5822,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5819,12 +5831,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.75)</t>
+          <t>group_total:21h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-111, 25-039, 23-055</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5844,15 +5856,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5866,7 +5882,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5875,12 +5891,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.57 (1.00-3.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 25-039, 23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5912,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5905,12 +5921,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.50-1.83)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5942,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5935,12 +5951,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.59 (0.31-1.05)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-077, 25-055, 25-039, 23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5972,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5965,12 +5981,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.62-0.75)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5986,21 +6002,21 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7.5</v>
+        <v>4.1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.50 (n=1)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23-055</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6016,21 +6032,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6050,15 +6066,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6072,21 +6092,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=2.00 (n=2)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-077, 25-039</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6122,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6111,12 +6131,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6152,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6141,12 +6161,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.00)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6162,21 +6182,21 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>18.3</v>
+        <v>7.6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=0.92 (n=2)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-077, 23-055</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6192,21 +6212,21 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>33.3</v>
+        <v>7.3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.39 (n=2)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-077, 23-055</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6222,21 +6242,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=0.20 (n=1)</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-077</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6252,21 +6272,21 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -6286,15 +6306,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6308,7 +6332,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.5</v>
+        <v>15.7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6317,12 +6341,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.38-0.92)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6362,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6347,12 +6371,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.00)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6368,21 +6392,21 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12.3</v>
+        <v>0.4</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>wc_ratio=0.82</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6402,15 +6426,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6424,7 +6452,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6433,12 +6461,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-2.50)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6482,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6463,12 +6491,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=0.57 (0.42-0.67)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6484,21 +6512,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.5</v>
+        <v>21.8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=1.58 (n=2)</t>
+          <t>group_total:56h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-039, 23-055</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6514,21 +6542,21 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.50-2.50)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6544,21 +6572,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>43.8</v>
+        <v>4.1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=0.73 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-077, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6574,21 +6602,21 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>49.3</v>
+        <v>5.5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=1.64 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-077, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6604,21 +6632,21 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=0.62 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-077, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6634,21 +6662,21 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8.199999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=1.03 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-077, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6664,21 +6692,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=0.40 (n=1)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-077</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6722,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12.5</v>
+        <v>22.4</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6703,12 +6731,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ratio=0.62 (0.40-1.10)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6724,21 +6752,21 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.7</v>
+        <v>11.2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=0.35 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-077, 25-039</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6754,21 +6782,21 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.8</v>
+        <v>22.2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=0.30 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-077, 25-039</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6784,21 +6812,21 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>wc_ratio=0.82</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6814,21 +6842,21 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>wc_ratio=0.82</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6872,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6853,12 +6881,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6874,21 +6902,21 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>wc_ratio=0.82</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6908,15 +6936,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6934,15 +6966,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6956,7 +6992,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6965,12 +7001,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6986,7 +7022,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>52</v>
+        <v>15.7</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6995,12 +7031,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ratio=1.73 (0.90-2.33)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -7020,15 +7056,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7046,15 +7086,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7068,21 +7112,21 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>34.2</v>
+        <v>27.1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ratio=0.95 (n=2)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>25-077, 25-039</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -7102,15 +7146,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7124,7 +7172,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7133,12 +7181,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ratio=4.00 (2.00-5.00)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -7158,15 +7206,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7180,7 +7232,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7189,12 +7241,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.50-3.00)</t>
+          <t>group_total:58h</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>25-077, 25-039, 23-055</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-083 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-083 GENERATED BUILD PLAN.xlsx
@@ -721,7 +721,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -832,7 +832,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -997,7 +997,7 @@
         <v>20</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>29.3</v>
+        <v>27.5</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1034,7 +1034,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1088,7 +1088,7 @@
         <v>20</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>group_total:9h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:9h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1233,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1303,7 +1303,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>10.8</v>
+        <v>7.3</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1340,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>9.9</v>
+        <v>6.7</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1427,7 +1427,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1464,7 +1464,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1501,7 +1501,7 @@
         <v>24</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1538,7 +1538,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1575,7 +1575,7 @@
         <v>5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1666,7 +1666,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1703,7 +1703,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1740,7 +1740,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1777,7 +1777,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1814,7 +1814,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1888,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2119,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2193,7 +2193,7 @@
         <v>6</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2284,7 +2284,7 @@
         <v>60</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2321,7 +2321,7 @@
         <v>30</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2432,7 +2432,7 @@
         <v>12</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2469,7 +2469,7 @@
         <v>20</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2506,7 +2506,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2543,7 +2543,7 @@
         <v>6</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2580,7 +2580,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2708,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2828,7 +2828,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2865,7 +2865,7 @@
         <v>30</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>15.7</v>
+        <v>12</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2968,7 +2968,7 @@
         <v>36</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>27.1</v>
+        <v>20.8</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -3055,7 +3055,7 @@
         <v>3</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3125,7 +3125,7 @@
         <v>6</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="I81" s="8" t="n"/>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>398</v>
+        <v>376.6</v>
       </c>
     </row>
   </sheetData>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:38h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29.3</v>
+        <v>27.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:9h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:9h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.8</v>
+        <v>7.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.9</v>
+        <v>6.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:21h</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:38h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>group_total:34h</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>group_total:56h</t>
+          <t>group_total:55h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>15.7</v>
+        <v>12</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>27.1</v>
+        <v>20.8</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>group_total:58h</t>
+          <t>group_total:44h</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
